--- a/kerntabellen/gemeente_refreg.xlsx
+++ b/kerntabellen/gemeente_refreg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\gebiedsniveaus\kerntabellen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\gebiedsniveaus\kerntabellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C6988B-EA5C-4710-8934-EC24E552AAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EC1BA8-9488-476F-B82E-414DFD951585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="3" r:id="rId1"/>
@@ -5002,10 +5002,10 @@
         <v>252</v>
       </c>
       <c r="C260" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D260" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
